--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486778_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486778_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7114</v>
+        <v>11.1016</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4892</v>
+        <v>6.8546</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2222</v>
+        <v>4.247</v>
       </c>
       <c r="G2" t="n">
         <v>5.2328</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.066</v>
+        <v>0.3242</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0548</v>
+        <v>0.4203</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1209</v>
+        <v>-0.096</v>
       </c>
       <c r="V2" t="n">
         <v>2.4554</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.3806</v>
+        <v>10.7984</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4552</v>
+        <v>5.9723</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9253</v>
+        <v>4.826</v>
       </c>
       <c r="G3" t="n">
         <v>9.585900000000001</v>
@@ -688,13 +688,13 @@
         <v>3.8616</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4797</v>
+        <v>-0.0619</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2763</v>
+        <v>0.2408</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2034</v>
+        <v>-0.3027</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6565</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>9.2386</v>
+        <v>8.8483</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6577</v>
+        <v>4.2426</v>
       </c>
       <c r="F4" t="n">
-        <v>5.5809</v>
+        <v>4.6057</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4423</v>
+        <v>5.2026</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7581</v>
+        <v>1.8546</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6842</v>
+        <v>3.348</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4921</v>
+        <v>3.0591</v>
       </c>
       <c r="K4" t="n">
-        <v>2.104</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3881</v>
+        <v>2.2381</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9502</v>
+        <v>2.1434</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6541</v>
+        <v>1.0335</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2961</v>
+        <v>1.1099</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>3.4754</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>3.4754</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7617</v>
+        <v>-0.3583</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1553</v>
+        <v>-0.3994</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4554</v>
+        <v>0.5286</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4554</v>
+        <v>1.1424</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>8.4457</v>
+        <v>8.249700000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5669</v>
+        <v>3.1406</v>
       </c>
       <c r="F5" t="n">
-        <v>4.8788</v>
+        <v>5.1091</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2026</v>
+        <v>5.4423</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8546</v>
+        <v>3.7581</v>
       </c>
       <c r="I5" t="n">
-        <v>3.348</v>
+        <v>1.6842</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0591</v>
+        <v>3.4921</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8211000000000001</v>
+        <v>2.104</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2381</v>
+        <v>1.3881</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1434</v>
+        <v>1.9502</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0335</v>
+        <v>1.6541</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1099</v>
+        <v>0.2961</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4754</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R5" t="n">
         <v>3.4754</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7609</v>
+        <v>-0.2272</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6347</v>
+        <v>0.0893</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1262</v>
+        <v>-0.3165</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5286</v>
+        <v>2.4554</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1424</v>
+        <v>2.4554</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5535</v>
+        <v>5.2859</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7009</v>
+        <v>3.0111</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8526</v>
+        <v>2.2748</v>
       </c>
       <c r="G6" t="n">
         <v>4.4651</v>
@@ -922,13 +922,13 @@
         <v>2.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2286</v>
+        <v>-1.4962</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7174</v>
+        <v>-0.4071</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5112</v>
+        <v>-1.0891</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6397</v>
+        <v>2.8883</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0943</v>
+        <v>2.2186</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5455</v>
+        <v>0.6696</v>
       </c>
       <c r="G7" t="n">
         <v>0.4183</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5995</v>
+        <v>0.8481</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6545</v>
+        <v>0.7789</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.055</v>
+        <v>0.0692</v>
       </c>
       <c r="V7" t="n">
         <v>0.6565</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0833</v>
+        <v>1.8557</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9188</v>
+        <v>0.8153</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1645</v>
+        <v>1.0404</v>
       </c>
       <c r="G8" t="n">
         <v>2.2371</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4414</v>
+        <v>0.2138</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.503</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.165</v>
+        <v>-0.2892</v>
       </c>
       <c r="V8" t="n">
         <v>1.1424</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>R. MONTECINO PARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0414</v>
+        <v>1.1227</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9346</v>
+        <v>0.7713</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8932</v>
+        <v>0.3514</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3235</v>
+        <v>-0.429</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.3102</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2403</v>
+        <v>-0.7392</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3808</v>
+        <v>0.1161</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6761</v>
+        <v>0.7242</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2953</v>
+        <v>-0.6081</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7043</v>
+        <v>-0.5451</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7593</v>
+        <v>-0.414</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.945</v>
+        <v>-0.1311</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8862</v>
+        <v>-0.0276</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2336</v>
+        <v>0.0413</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3474</v>
+        <v>-0.0689</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MONTECINO PARRA</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9351</v>
+        <v>0.8129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5092</v>
+        <v>0.0684</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4259</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.429</v>
+        <v>0.5095</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3102</v>
+        <v>0.4688</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7392</v>
+        <v>0.0407</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1161</v>
+        <v>0.7856</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7242</v>
+        <v>0.7449</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6081</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5451</v>
+        <v>-0.2761</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.414</v>
+        <v>-0.2761</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1311</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2151</v>
+        <v>0.3034</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2207</v>
+        <v>0.2481</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0056</v>
+        <v>0.0552</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4489</v>
+        <v>-0.0244</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3453</v>
+        <v>0.6453</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7942</v>
+        <v>-0.6697</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5095</v>
+        <v>-1.3235</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4688</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0407</v>
+        <v>-2.2403</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7856</v>
+        <v>0.3808</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7449</v>
+        <v>1.6761</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0407</v>
+        <v>-1.2953</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2761</v>
+        <v>-1.7043</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2761</v>
+        <v>-0.7593</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0606</v>
+        <v>0.8204</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1655</v>
+        <v>0.9443</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1049</v>
+        <v>-0.1239</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7205</v>
+        <v>-0.4102</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7931</v>
+        <v>-0.4829</v>
       </c>
       <c r="F12" t="n">
         <v>0.0727</v>
@@ -1390,10 +1390,10 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1654</v>
+        <v>0.1448</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1655</v>
+        <v>0.1447</v>
       </c>
       <c r="U12" t="n">
         <v>0.0001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6764</v>
+        <v>-1.1715</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4917</v>
+        <v>-1.2849</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1847</v>
+        <v>0.1133</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6925</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5294</v>
+        <v>1.0342</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.8133</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.077</v>
+        <v>0.221</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2856</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>49.0813</v>
+        <v>49.35739999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>25.6967</v>
+        <v>25.97229999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>23.3847</v>
+        <v>23.3848</v>
       </c>
       <c r="G14" t="n">
         <v>28.3792</v>
@@ -1525,7 +1525,7 @@
         <v>17.5923</v>
       </c>
       <c r="L14" t="n">
-        <v>7.178500000000002</v>
+        <v>7.178500000000001</v>
       </c>
       <c r="M14" t="n">
         <v>3.608700000000001</v>
@@ -1534,7 +1534,7 @@
         <v>4.129</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5203</v>
+        <v>-0.5202999999999995</v>
       </c>
       <c r="P14" t="n">
         <v>12.55</v>
@@ -1546,16 +1546,16 @@
         <v>25.1002</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2419</v>
+        <v>1.5177</v>
       </c>
       <c r="T14" t="n">
-        <v>3.582</v>
+        <v>3.858</v>
       </c>
       <c r="U14" t="n">
         <v>-2.3402</v>
       </c>
       <c r="V14" t="n">
-        <v>6.910000000000001</v>
+        <v>6.91</v>
       </c>
       <c r="W14" t="n">
         <v>9.8939</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SOTO RODRIGUEZ</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6338</v>
+        <v>-0.1676</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4491</v>
+        <v>0.112</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8153</v>
+        <v>-0.2795</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8146</v>
+        <v>0.5702</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8621</v>
+        <v>-0.9512</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0476</v>
+        <v>1.5214</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3198</v>
+        <v>1.4471</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2768</v>
+        <v>0.2218</v>
       </c>
       <c r="L15" t="n">
-        <v>0.043</v>
+        <v>1.2253</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5052</v>
+        <v>-0.8769</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4147</v>
+        <v>-1.173</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0905</v>
+        <v>0.2961</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1931</v>
+        <v>0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2979</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9096</v>
+        <v>-0.4623</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6117</v>
+        <v>-0.4686</v>
       </c>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.2856</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.5712</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.8568</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>I. SOTO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.131</v>
+        <v>-0.4363</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4005</v>
+        <v>2.4148</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5315</v>
+        <v>-2.8512</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8133</v>
+        <v>0.8146</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3235</v>
+        <v>0.8621</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4898</v>
+        <v>-0.0476</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1597</v>
+        <v>3.3198</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8492</v>
+        <v>3.2768</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6895</v>
+        <v>0.043</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.973</v>
+        <v>-2.5052</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1727</v>
+        <v>-2.4147</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8003</v>
+        <v>-0.0905</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1931</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4892</v>
+        <v>-0.7722</v>
       </c>
       <c r="T16" t="n">
-        <v>1.627</v>
+        <v>-0.1246</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1378</v>
+        <v>-0.6476</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6654</v>
+        <v>-0.9584</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1983</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4671</v>
+        <v>-1.5315</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5702</v>
+        <v>-1.8133</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9512</v>
+        <v>-0.3235</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5214</v>
+        <v>-1.4898</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4471</v>
+        <v>0.1597</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2218</v>
+        <v>0.8492</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2253</v>
+        <v>-0.6895</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8769</v>
+        <v>-1.973</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.173</v>
+        <v>-1.1727</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2961</v>
+        <v>-0.8003</v>
       </c>
       <c r="P17" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4287</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7725</v>
+        <v>0.7996</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6561</v>
+        <v>-0.1378</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SOTO MADRIGAL</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6415</v>
+        <v>-1.5628</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8481</v>
+        <v>-1.6528</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7934</v>
+        <v>0.09</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1658</v>
+        <v>-3.5709</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0414</v>
+        <v>-3.2138</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1244</v>
+        <v>-0.3571</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6274</v>
+        <v>-2.8251</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6274</v>
+        <v>-1.9029</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.9222</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5384</v>
+        <v>-0.7458</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.414</v>
+        <v>-1.3109</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1244</v>
+        <v>0.5651</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4412</v>
+        <v>0.1585</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2207</v>
+        <v>0.2961</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2204</v>
+        <v>-0.1377</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>1.2703</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>D. SOTO MADRIGAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7916</v>
+        <v>-2.6278</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5836</v>
+        <v>-0.8481</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.208</v>
+        <v>-1.7797</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5709</v>
+        <v>-1.1658</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.2138</v>
+        <v>-1.0414</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3571</v>
+        <v>-0.1244</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.8251</v>
+        <v>-0.6274</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9029</v>
+        <v>-0.6274</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9222</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7458</v>
+        <v>-0.5384</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3109</v>
+        <v>-0.414</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5651</v>
+        <v>-0.1244</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0703</v>
+        <v>-0.4274</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6347</v>
+        <v>-0.2207</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4356</v>
+        <v>-0.2067</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2703</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3011</v>
+        <v>-3.1728</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.531</v>
+        <v>-1.4275</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7701</v>
+        <v>-1.7453</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4421</v>
@@ -2014,13 +2014,13 @@
         <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8937</v>
+        <v>-0.7654</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4966</v>
+        <v>-0.3932</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.397</v>
+        <v>-0.3722</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.496</v>
+        <v>-3.9982</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5943</v>
+        <v>-2.284</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9017</v>
+        <v>-1.7141</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6232</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8148</v>
+        <v>-1.317</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8829</v>
+        <v>-0.5726</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9319</v>
+        <v>-0.7444</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4458</v>
+        <v>-4.8279</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3801</v>
+        <v>-3.1733</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0657</v>
+        <v>-1.6547</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9192</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6384</v>
+        <v>-1.0205</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7174</v>
+        <v>-0.5105</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9211</v>
+        <v>-0.51</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5712</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2414</v>
+        <v>-5.1905</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0236</v>
+        <v>-1.1962</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2178</v>
+        <v>-3.9943</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1284</v>
@@ -2248,13 +2248,13 @@
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7615</v>
+        <v>0.2894</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2763</v>
+        <v>0.5511</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4852</v>
+        <v>-0.2617</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0766</v>
+        <v>-7.6393</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9803</v>
+        <v>-2.394</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.0963</v>
+        <v>-5.2453</v>
       </c>
       <c r="G24" t="n">
         <v>-3.8018</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5554</v>
+        <v>0.9927</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3786</v>
+        <v>0.9649</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1768</v>
+        <v>0.0278</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1271</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.098800000000001</v>
+        <v>-8.784700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5736</v>
+        <v>-5.8799</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5251</v>
+        <v>-2.9047</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.8429</v>
+        <v>-5.4566</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.2197</v>
+        <v>-5.192</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6232</v>
+        <v>-0.2645</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.2696</v>
+        <v>-1.7793</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.3917</v>
+        <v>-2.4327</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1221</v>
+        <v>0.6534</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5733</v>
+        <v>-3.6772</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.828</v>
+        <v>-2.7593</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7453</v>
+        <v>-0.9179</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1585</v>
+        <v>-3.4754</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.3169</v>
+        <v>-5.2131</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4159</v>
+        <v>1.0894</v>
       </c>
       <c r="T25" t="n">
-        <v>2.0129</v>
+        <v>0.8269</v>
       </c>
       <c r="U25" t="n">
-        <v>0.403</v>
+        <v>0.2625</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.5133</v>
+        <v>-0.9421</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.825900000000001</v>
+        <v>-9.025499999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.2936</v>
+        <v>-6.401</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5323</v>
+        <v>-2.6244</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.4566</v>
+        <v>-7.8429</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.192</v>
+        <v>-6.2197</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2645</v>
+        <v>-1.6232</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.7793</v>
+        <v>-5.2696</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.4327</v>
+        <v>-5.3917</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6534</v>
+        <v>0.1221</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.6772</v>
+        <v>-2.5733</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.7593</v>
+        <v>-0.828</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9179</v>
+        <v>-1.7453</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.4754</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.2131</v>
+        <v>-2.3169</v>
       </c>
       <c r="R26" t="n">
-        <v>1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0482</v>
+        <v>1.4892</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4132</v>
+        <v>1.1855</v>
       </c>
       <c r="U26" t="n">
-        <v>0.635</v>
+        <v>0.3037</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9421</v>
+        <v>-1.5133</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-49.0813</v>
+        <v>-48.3918</v>
       </c>
       <c r="E27" t="n">
         <v>-22.1569</v>
       </c>
       <c r="F27" t="n">
-        <v>-26.9243</v>
+        <v>-26.2347</v>
       </c>
       <c r="G27" t="n">
         <v>-28.3794</v>
@@ -2560,16 +2560,16 @@
         <v>12.55</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.241999999999999</v>
+        <v>-0.5524000000000002</v>
       </c>
       <c r="T27" t="n">
         <v>2.3402</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.582000000000001</v>
+        <v>-2.8927</v>
       </c>
       <c r="V27" t="n">
-        <v>-6.91</v>
+        <v>-6.910000000000001</v>
       </c>
       <c r="W27" t="n">
         <v>4.2116</v>
